--- a/final_data_pipeline/output/325194_elec_options.xlsx
+++ b/final_data_pipeline/output/325194_elec_options.xlsx
@@ -882,7 +882,7 @@
         <v>102</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -977,7 +977,7 @@
         <v>102</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1072,7 +1072,7 @@
         <v>102</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1167,7 +1167,7 @@
         <v>102</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1262,7 +1262,7 @@
         <v>102</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1357,7 +1357,7 @@
         <v>102</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1452,7 +1452,7 @@
         <v>102</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1547,7 +1547,7 @@
         <v>102</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1642,7 +1642,7 @@
         <v>102</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1737,7 +1737,7 @@
         <v>102</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1832,7 +1832,7 @@
         <v>102</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1927,7 +1927,7 @@
         <v>102</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>102</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2117,7 +2117,7 @@
         <v>102</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2212,7 +2212,7 @@
         <v>102</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2307,7 +2307,7 @@
         <v>102</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2402,7 +2402,7 @@
         <v>102</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2497,7 +2497,7 @@
         <v>103</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2592,7 +2592,7 @@
         <v>103</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2687,7 +2687,7 @@
         <v>103</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2782,7 +2782,7 @@
         <v>103</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2877,7 +2877,7 @@
         <v>103</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2972,7 +2972,7 @@
         <v>103</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -3067,7 +3067,7 @@
         <v>102</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -5065,7 +5065,7 @@
         <v>103</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5163,7 +5163,7 @@
         <v>103</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE47">
         <v>8000</v>
@@ -5261,7 +5261,7 @@
         <v>103</v>
       </c>
       <c r="AD48">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE48">
         <v>8000</v>
@@ -5356,7 +5356,7 @@
         <v>102</v>
       </c>
       <c r="AD49">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE49">
         <v>8000</v>
@@ -5451,7 +5451,7 @@
         <v>103</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5546,7 +5546,7 @@
         <v>102</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5641,7 +5641,7 @@
         <v>102</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5736,7 +5736,7 @@
         <v>102</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5831,7 +5831,7 @@
         <v>102</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5926,7 +5926,7 @@
         <v>102</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6021,7 +6021,7 @@
         <v>103</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -7636,7 +7636,7 @@
         <v>102</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7731,7 +7731,7 @@
         <v>102</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -7826,7 +7826,7 @@
         <v>103</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -7921,7 +7921,7 @@
         <v>102</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -8396,7 +8396,7 @@
         <v>102</v>
       </c>
       <c r="AD81">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE81">
         <v>8000</v>
@@ -8491,7 +8491,7 @@
         <v>102</v>
       </c>
       <c r="AD82">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE82">
         <v>8000</v>
@@ -8586,7 +8586,7 @@
         <v>102</v>
       </c>
       <c r="AD83">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE83">
         <v>8000</v>
@@ -8681,7 +8681,7 @@
         <v>102</v>
       </c>
       <c r="AD84">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE84">
         <v>8000</v>
@@ -8776,7 +8776,7 @@
         <v>102</v>
       </c>
       <c r="AD85">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE85">
         <v>8000</v>
@@ -8871,7 +8871,7 @@
         <v>102</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE86">
         <v>8000</v>
@@ -8966,7 +8966,7 @@
         <v>102</v>
       </c>
       <c r="AD87">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE87">
         <v>8000</v>
@@ -9061,7 +9061,7 @@
         <v>102</v>
       </c>
       <c r="AD88">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE88">
         <v>8000</v>
@@ -9156,7 +9156,7 @@
         <v>102</v>
       </c>
       <c r="AD89">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE89">
         <v>8000</v>
@@ -9251,7 +9251,7 @@
         <v>102</v>
       </c>
       <c r="AD90">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE90">
         <v>8000</v>
@@ -9346,7 +9346,7 @@
         <v>102</v>
       </c>
       <c r="AD91">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE91">
         <v>8000</v>
@@ -9441,7 +9441,7 @@
         <v>103</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9536,7 +9536,7 @@
         <v>103</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9631,7 +9631,7 @@
         <v>103</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9726,7 +9726,7 @@
         <v>103</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9821,7 +9821,7 @@
         <v>103</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9916,7 +9916,7 @@
         <v>103</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -10011,7 +10011,7 @@
         <v>103</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -10106,7 +10106,7 @@
         <v>102</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -10201,7 +10201,7 @@
         <v>102</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -10296,7 +10296,7 @@
         <v>102</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -10391,7 +10391,7 @@
         <v>102</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -10486,7 +10486,7 @@
         <v>102</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10581,7 +10581,7 @@
         <v>102</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10676,7 +10676,7 @@
         <v>102</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -10771,7 +10771,7 @@
         <v>102</v>
       </c>
       <c r="AD106">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE106">
         <v>8000</v>
@@ -10866,7 +10866,7 @@
         <v>102</v>
       </c>
       <c r="AD107">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE107">
         <v>8000</v>
@@ -10961,7 +10961,7 @@
         <v>102</v>
       </c>
       <c r="AD108">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE108">
         <v>8000</v>
